--- a/九龙-茶果岭、油塘及鲤鱼门-蔚蓝东岸/蔚蓝东岸_销控明细表.xlsx
+++ b/九龙-茶果岭、油塘及鲤鱼门-蔚蓝东岸/蔚蓝东岸_销控明细表.xlsx
@@ -14025,7 +14025,7 @@
       </c>
       <c r="F198" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G198" s="3" t="inlineStr">
@@ -15031,7 +15031,7 @@
       </c>
       <c r="F213" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G213" s="3" t="inlineStr">
@@ -48665,12 +48665,12 @@
           <t>7</t>
         </is>
       </c>
-      <c r="B20" s="25" t="inlineStr">
+      <c r="B20" s="23" t="inlineStr">
         <is>
           <t>A | 1057呎 (4+房)
 招标单位
 -
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="C20" s="22" t="inlineStr">
@@ -48806,12 +48806,12 @@
           <t>3</t>
         </is>
       </c>
-      <c r="B23" s="25" t="inlineStr">
+      <c r="B23" s="23" t="inlineStr">
         <is>
           <t>A | 1057呎 (4+房)
 招标单位
 -
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="C23" s="24" t="inlineStr">
